--- a/Prediction Market Tracking.xlsx
+++ b/Prediction Market Tracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdl11\Desktop\VPM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CC718C-6382-474E-B5E3-505F733E11BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B77FD5-21F2-4CEC-B2A1-41D018178C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -964,7 +964,7 @@
         <v>0.3</v>
       </c>
       <c r="G4" s="7">
-        <f t="shared" ref="G4:G53" si="0">IF(E4="","",E4-F4)</f>
+        <f t="shared" ref="G4:G35" si="0">IF(E4="","",E4-F4)</f>
         <v>9.2000000000000026E-2</v>
       </c>
       <c r="H4" s="6">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="17">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="17">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,14 +2886,14 @@
       </c>
       <c r="B8" s="14">
         <f>$C$3*0.7</f>
-        <v>24.5</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="19">
         <f>$C$3*0.7</f>
-        <v>24.5</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>48</v>
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B10" s="14">
         <f>$C$3*1.1</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>54</v>
       </c>
       <c r="D10" s="19">
         <f>$C$3</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>55</v>
@@ -2941,14 +2941,14 @@
       </c>
       <c r="B11" s="14">
         <f>$C$3*1.2</f>
-        <v>42</v>
+        <v>55.199999999999996</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="19">
         <f>$C$3*1.1</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>55</v>
@@ -2987,18 +2987,18 @@
       </c>
       <c r="B15" s="14">
         <f>IF($C$3*1.1&gt;0,$C$3*1.1,"")</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="23">
         <f>$C$3*0.85</f>
-        <v>29.75</v>
+        <v>39.1</v>
       </c>
       <c r="E15" s="14" t="str">
         <f>IF($C$3*0.85&gt;0,"Price drops to "&amp;TEXT($C$3*0.85,"0.00")&amp;"c","")</f>
-        <v>Price drops to 29.75c</v>
+        <v>Price drops to 39.10c</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -3007,18 +3007,18 @@
       </c>
       <c r="B16" s="14">
         <f>$C$3*1.1</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="23">
         <f>$C$3</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E16" s="14" t="str">
         <f>IF($C$3&gt;0,"Price drops to "&amp;TEXT($C$3,"0.00")&amp;"c","")</f>
-        <v>Price drops to 35.00c</v>
+        <v>Price drops to 46.00c</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3027,18 +3027,18 @@
       </c>
       <c r="B17" s="14">
         <f>$C$3*1.2</f>
-        <v>42</v>
+        <v>55.199999999999996</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="23">
         <f>$C$3*1.1</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
       <c r="E17" s="14" t="str">
         <f>IF($C$3*1.1&gt;0,"Price drops to "&amp;TEXT($C$3*1.1,"0.00")&amp;"c","")</f>
-        <v>Price drops to 38.50c</v>
+        <v>Price drops to 50.60c</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3047,18 +3047,18 @@
       </c>
       <c r="B18" s="14">
         <f>$C$3*1.3</f>
-        <v>45.5</v>
+        <v>59.800000000000004</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D18" s="23">
         <f>$C$4*0.9</f>
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E18" s="14" t="str">
         <f>IF($C$4*0.9&gt;0,"Price drops to "&amp;TEXT($C$4*0.9,"0.00")&amp;"c","")</f>
-        <v>Price drops to 64.80c</v>
+        <v>Price drops to 62.10c</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3067,18 +3067,18 @@
       </c>
       <c r="B19" s="14">
         <f>$C$3*1.4</f>
-        <v>49</v>
+        <v>64.399999999999991</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D19" s="23">
         <f>$C$4*0.9</f>
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E19" s="14" t="str">
         <f>IF($C$4*0.9&gt;0,"Price drops to "&amp;TEXT($C$4*0.9,"0.00")&amp;"c","")</f>
-        <v>Price drops to 64.80c</v>
+        <v>Price drops to 62.10c</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3087,18 +3087,18 @@
       </c>
       <c r="B20" s="14">
         <f>$C$3*1.5</f>
-        <v>52.5</v>
+        <v>69</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D20" s="23">
         <f>$C$4*0.9</f>
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E20" s="14" t="str">
         <f>IF($C$4*0.9&gt;0,"Price drops to "&amp;TEXT($C$4*0.9,"0.00")&amp;"c","")</f>
-        <v>Price drops to 64.80c</v>
+        <v>Price drops to 62.10c</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B24" s="24">
         <f>$C$3*0.7</f>
-        <v>24.5</v>
+        <v>32.199999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B25" s="24">
         <f>$C$3*0.85</f>
-        <v>29.75</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B26" s="24">
         <f>$C$3</f>
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B27" s="24">
         <f>$C$3*1.1</f>
-        <v>38.5</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B28" s="24">
         <f>$C$3*1.2</f>
-        <v>42</v>
+        <v>55.199999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B29" s="24">
         <f>$C$4*0.9</f>
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
     </row>
   </sheetData>
